--- a/site/exports/nudt-computer.xlsx
+++ b/site/exports/nudt-computer.xlsx
@@ -452,7 +452,7 @@
     <col width="25.2" customWidth="1" min="4" max="4"/>
     <col width="16" customWidth="1" min="5" max="5"/>
     <col width="65" customWidth="1" min="6" max="6"/>
-    <col width="18.2" customWidth="1" min="7" max="7"/>
+    <col width="37.8" customWidth="1" min="7" max="7"/>
     <col width="44.8" customWidth="1" min="8" max="8"/>
     <col width="23.8" customWidth="1" min="9" max="9"/>
     <col width="16" customWidth="1" min="10" max="10"/>
@@ -482,7 +482,7 @@
       </c>
       <c r="E1" s="1" t="inlineStr">
         <is>
-          <t>核对日期</t>
+          <t>已记录来源检索日期</t>
         </is>
       </c>
       <c r="F1" s="1" t="inlineStr">
@@ -535,7 +535,7 @@
       <c r="D2" s="2" t="inlineStr"/>
       <c r="E2" s="2" t="inlineStr">
         <is>
-          <t>2026-10-23</t>
+          <t>2026-10-24</t>
         </is>
       </c>
       <c r="F2" s="2" t="inlineStr">
@@ -545,7 +545,7 @@
       </c>
       <c r="G2" s="2" t="inlineStr">
         <is>
-          <t>分批核实资料，不是完整名录</t>
+          <t>分批核实资料，不是完整名录；人物整体核验日期未单独记录</t>
         </is>
       </c>
       <c r="H2" s="2" t="inlineStr">
@@ -584,7 +584,7 @@
       <c r="D3" s="2" t="inlineStr"/>
       <c r="E3" s="2" t="inlineStr">
         <is>
-          <t>2026-10-23</t>
+          <t>2026-10-24</t>
         </is>
       </c>
       <c r="F3" s="2" t="inlineStr">
@@ -594,7 +594,7 @@
       </c>
       <c r="G3" s="2" t="inlineStr">
         <is>
-          <t>分批核实资料，不是完整名录</t>
+          <t>分批核实资料，不是完整名录；人物整体核验日期未单独记录</t>
         </is>
       </c>
       <c r="H3" s="2" t="inlineStr">
@@ -633,7 +633,7 @@
       <c r="D4" s="2" t="inlineStr"/>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>2026-10-23</t>
+          <t>2026-10-24</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
@@ -643,7 +643,7 @@
       </c>
       <c r="G4" s="2" t="inlineStr">
         <is>
-          <t>分批核实资料，不是完整名录</t>
+          <t>分批核实资料，不是完整名录；人物整体核验日期未单独记录</t>
         </is>
       </c>
       <c r="H4" s="2" t="inlineStr">
